--- a/data/Population_bg_2009_2025.xlsx
+++ b/data/Population_bg_2009_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://xellagroup-my.sharepoint.com/personal/boris_yotsov_xella_com/Documents/U_Drive/Privat/3.PC/Data_Science/12.Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="11_AD4DF75460589B3ACB728432C71D4FCA5ADEDD97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F5C4B9C-2A84-4A01-B3F4-1B33385FA721}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="11_AD4DF75460589B3ACB728432C71D4FCA5ADEDD97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14C686A2-F75C-44B6-BD88-62C91A610591}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,15 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t xml:space="preserve">Year </t>
   </si>
   <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t>7 563 710 </t>
   </si>
 </sst>
 </file>
@@ -383,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
@@ -399,7 +396,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B2" s="2">
         <v>6437360</v>
@@ -407,146 +404,137 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <f t="shared" ref="A3:A18" si="0">A2-1</f>
-        <v>2024</v>
+        <f t="shared" ref="A3:A17" si="0">A2-1</f>
+        <v>2023</v>
       </c>
       <c r="B3" s="2">
-        <v>6778993</v>
+        <v>6445481</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f t="shared" si="0"/>
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B4" s="2">
-        <v>6827262</v>
+        <v>6447710</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B5" s="2">
-        <v>6875874</v>
+        <v>6507301</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B6" s="2">
-        <v>6519789</v>
+        <v>6550696</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B7" s="2">
-        <v>7311869</v>
+        <v>6616726</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B8" s="2">
-        <v>6951482</v>
+        <v>6710798</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B9" s="2">
-        <v>7000000</v>
+        <v>6803468</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B10" s="2">
-        <v>7126997</v>
+        <v>6894139</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B11" s="2">
-        <v>7175713</v>
+        <v>6984225</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B12" s="2">
-        <v>7222505</v>
+        <v>7073572</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B13" s="2">
-        <v>7267687</v>
+        <v>7160005</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B14" s="2">
-        <v>7311869</v>
+        <v>7305888</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <f t="shared" si="0"/>
-        <v>2012</v>
+        <f>A14-1</f>
+        <v>2011</v>
       </c>
       <c r="B15" s="2">
-        <v>7356208</v>
+        <v>7348328</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <f>A15-1</f>
-        <v>2011</v>
+        <f t="shared" si="0"/>
+        <v>2010</v>
       </c>
       <c r="B16" s="2">
-        <v>7401641</v>
+        <v>7395599</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B17" s="2">
-        <v>7449061</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <f t="shared" si="0"/>
-        <v>2009</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>2</v>
+        <v>7444443</v>
       </c>
     </row>
   </sheetData>
